--- a/verification/cases/roundtrip/number_formats/init.xlsx
+++ b/verification/cases/roundtrip/number_formats/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10323"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonyschott/repos/poi/test-data/spreadsheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD7B4B2-CA35-6F43-BBA5-C98D4633A221}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E90894D-4735-4C85-AE43-6712F07CFCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33140" windowHeight="22740" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flags" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,17 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -535,7 +546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -565,9 +576,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -912,15 +920,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="7"/>
+    <col min="1" max="1" width="10.6328125" style="7"/>
     <col min="2" max="2" width="17" style="8" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" style="8" customWidth="1"/>
-    <col min="4" max="16384" width="10.6640625" style="1"/>
+    <col min="3" max="3" width="34.81640625" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
@@ -931,7 +939,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>72</v>
       </c>
@@ -939,7 +947,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>78</v>
       </c>
@@ -948,7 +956,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>80</v>
       </c>
@@ -974,16 +982,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D337"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="10.6640625" style="2"/>
+    <col min="5" max="16384" width="10.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>103</v>
       </c>
@@ -997,7 +1005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="str">
         <f>TEXT(C2, B2)</f>
         <v>12.34</v>
@@ -1012,7 +1020,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="str">
         <f t="shared" ref="A3:A152" si="0">TEXT(C3, B3)</f>
         <v>12.3</v>
@@ -1027,7 +1035,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="str">
         <f t="shared" si="0"/>
         <v>012.30</v>
@@ -1042,7 +1050,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="str">
         <f t="shared" si="0"/>
         <v>£012.30</v>
@@ -1057,7 +1065,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="str">
         <f t="shared" ref="A6:A10" si="1">TEXT(C6, B6)</f>
         <v>12.3</v>
@@ -1072,7 +1080,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="str">
         <f t="shared" si="1"/>
         <v>12.3</v>
@@ -1087,7 +1095,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="str">
         <f t="shared" si="1"/>
         <v>$12.3</v>
@@ -1102,7 +1110,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="str">
         <f t="shared" si="1"/>
         <v>$12.3</v>
@@ -1117,7 +1125,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="str">
         <f t="shared" si="1"/>
         <v>$12.30</v>
@@ -1132,7 +1140,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-12.3</v>
@@ -1147,7 +1155,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-12.3</v>
@@ -1162,7 +1170,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-$12.3</v>
@@ -1177,7 +1185,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-$12.3</v>
@@ -1192,7 +1200,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-$12.30</v>
@@ -1207,11 +1215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="str">
         <f t="shared" ref="A17:A19" si="2">TEXT(C17, B17)</f>
         <v>a $12.30 profit</v>
@@ -1226,7 +1230,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="str">
         <f t="shared" si="2"/>
         <v>¥12.30 after</v>
@@ -1241,7 +1245,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="str">
         <f t="shared" si="2"/>
         <v>before ¥12.30</v>
@@ -1256,7 +1260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-a $12.30 profit</v>
@@ -1271,7 +1275,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-¥12.30 after</v>
@@ -1286,7 +1290,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-before ¥12.30</v>
@@ -1301,7 +1305,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="str">
         <f t="shared" ref="A24:A39" si="3">TEXT(C24, B24)</f>
         <v>1,234,567</v>
@@ -1316,7 +1320,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567</v>
@@ -1331,7 +1335,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567</v>
@@ -1346,7 +1350,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="str">
         <f t="shared" si="3"/>
         <v>,1234567</v>
@@ -1361,7 +1365,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567.</v>
@@ -1376,7 +1380,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567</v>
@@ -1391,7 +1395,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567</v>
@@ -1406,7 +1410,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567</v>
@@ -1421,7 +1425,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="str">
         <f t="shared" si="3"/>
         <v>,1234567</v>
@@ -1436,7 +1440,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567.0</v>
@@ -1451,7 +1455,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="str">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -1466,7 +1470,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="str">
         <f t="shared" si="3"/>
         <v>123</v>
@@ -1481,7 +1485,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234</v>
@@ -1496,7 +1500,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="str">
         <f t="shared" si="3"/>
         <v>12,345</v>
@@ -1511,7 +1515,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="str">
         <f t="shared" si="3"/>
         <v>123,456</v>
@@ -1526,7 +1530,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="str">
         <f t="shared" si="3"/>
         <v>1,234,567</v>
@@ -1541,7 +1545,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="str">
         <f t="shared" ref="A40:A46" si="4">TEXT(C40, B40)</f>
         <v>1,234,567</v>
@@ -1556,7 +1560,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="str">
         <f t="shared" si="4"/>
         <v>1,234,567</v>
@@ -1571,7 +1575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="str">
         <f t="shared" si="4"/>
         <v>1,234,567</v>
@@ -1586,7 +1590,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="str">
         <f t="shared" si="4"/>
         <v>1,234,567</v>
@@ -1601,7 +1605,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> 1,234,567</v>
@@ -1616,7 +1620,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  1,234,567</v>
@@ -1631,7 +1635,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">    1,234,567</v>
@@ -1646,7 +1650,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="str">
         <f t="shared" ref="A47:A52" si="5">TEXT(C47, B47)</f>
         <v>12</v>
@@ -1661,7 +1665,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="str">
         <f t="shared" si="5"/>
         <v>123</v>
@@ -1676,7 +1680,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="str">
         <f t="shared" si="5"/>
         <v>1,234</v>
@@ -1691,7 +1695,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="str">
         <f t="shared" si="5"/>
         <v>12,345</v>
@@ -1706,7 +1710,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="str">
         <f t="shared" si="5"/>
         <v>123,456</v>
@@ -1721,7 +1725,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="str">
         <f t="shared" si="5"/>
         <v>1,234,567</v>
@@ -1736,7 +1740,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567</v>
@@ -1751,7 +1755,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567</v>
@@ -1766,7 +1770,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567</v>
@@ -1781,7 +1785,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-,1234567</v>
@@ -1796,7 +1800,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567.</v>
@@ -1811,7 +1815,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567</v>
@@ -1826,7 +1830,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567</v>
@@ -1841,7 +1845,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567</v>
@@ -1856,7 +1860,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-,1234567</v>
@@ -1871,7 +1875,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1,234,567.0</v>
@@ -1886,7 +1890,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="str">
         <f t="shared" ref="A63:A69" si="6">TEXT(C63, B63)</f>
         <v>1,234,567</v>
@@ -1901,7 +1905,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="str">
         <f t="shared" si="6"/>
         <v>1,234,567</v>
@@ -1916,7 +1920,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="str">
         <f t="shared" si="6"/>
         <v>1,234,567</v>
@@ -1931,7 +1935,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="str">
         <f t="shared" si="6"/>
         <v>1,234,567</v>
@@ -1946,7 +1950,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="str">
         <f t="shared" si="6"/>
         <v>01,234,567</v>
@@ -1961,7 +1965,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="str">
         <f t="shared" si="6"/>
         <v>001,234,567</v>
@@ -1976,7 +1980,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="9" t="str">
         <f t="shared" si="6"/>
         <v>0,001,234,567</v>
@@ -1991,7 +1995,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="9" t="str">
         <f t="shared" ref="A70:A75" si="7">TEXT(C70, B70)</f>
         <v>-12</v>
@@ -2006,7 +2010,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="str">
         <f t="shared" si="7"/>
         <v>-123</v>
@@ -2021,7 +2025,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="str">
         <f t="shared" si="7"/>
         <v>-1,234</v>
@@ -2036,7 +2040,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="str">
         <f t="shared" si="7"/>
         <v>-12,345</v>
@@ -2051,7 +2055,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="str">
         <f t="shared" si="7"/>
         <v>-123,456</v>
@@ -2066,7 +2070,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="str">
         <f t="shared" si="7"/>
         <v>-1,234,567</v>
@@ -2081,7 +2085,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="str">
         <f t="shared" ref="A76:A82" si="8">TEXT(C76, B76)</f>
         <v>-1,234,567</v>
@@ -2096,7 +2100,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="str">
         <f t="shared" si="8"/>
         <v>-1,234,567</v>
@@ -2111,7 +2115,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="str">
         <f t="shared" si="8"/>
         <v>-1,234,567</v>
@@ -2126,7 +2130,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="str">
         <f t="shared" si="8"/>
         <v>-1,234,567</v>
@@ -2141,7 +2145,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="str">
         <f t="shared" si="8"/>
         <v>- 1,234,567</v>
@@ -2156,7 +2160,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="str">
         <f t="shared" si="8"/>
         <v>-  1,234,567</v>
@@ -2171,7 +2175,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="str">
         <f t="shared" si="8"/>
         <v>-    1,234,567</v>
@@ -2186,7 +2190,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="9" t="str">
         <f t="shared" ref="A83:A91" si="9">TEXT(C83, B83)</f>
         <v>-12</v>
@@ -2201,7 +2205,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="9" t="str">
         <f t="shared" si="9"/>
         <v>-123</v>
@@ -2216,7 +2220,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="9" t="str">
         <f t="shared" si="9"/>
         <v>-1,234</v>
@@ -2231,7 +2235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="9" t="str">
         <f t="shared" si="9"/>
         <v>-12,345</v>
@@ -2246,7 +2250,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="9" t="str">
         <f t="shared" si="9"/>
         <v>-123,456</v>
@@ -2261,7 +2265,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="9" t="str">
         <f t="shared" si="9"/>
         <v>-1,234,567</v>
@@ -2276,7 +2280,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="9" t="str">
         <f t="shared" si="9"/>
         <v>1235</v>
@@ -2291,7 +2295,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="9" t="str">
         <f t="shared" si="9"/>
         <v>1</v>
@@ -2306,7 +2310,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="9" t="str">
         <f t="shared" ref="A92:A93" si="10">TEXT(C92, B92)</f>
         <v>1234.6</v>
@@ -2321,7 +2325,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="9" t="str">
         <f t="shared" si="10"/>
         <v>1.2</v>
@@ -2336,7 +2340,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1235</v>
@@ -2351,7 +2355,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2366,7 +2370,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1234.6</v>
@@ -2381,7 +2385,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-1.2</v>
@@ -2396,12 +2400,10 @@
         <v>68</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D98" s="7"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="9" t="str">
         <f t="shared" ref="A99:A101" si="11">TEXT(C99, B99)</f>
         <v>1.23%</v>
@@ -2416,7 +2418,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="9" t="str">
         <f t="shared" si="11"/>
         <v>12,345.00%</v>
@@ -2431,7 +2433,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="9" t="str">
         <f t="shared" si="11"/>
         <v>1,234,500.00%%</v>
@@ -2446,7 +2448,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="9" t="str">
         <f>TEXT(C102, B102)</f>
         <v>-1.23%</v>
@@ -2461,7 +2463,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="9" t="str">
         <f>TEXT(C103, B103)</f>
         <v>-12,345.00%</v>
@@ -2476,7 +2478,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="9" t="str">
         <f>TEXT(C104, B104)</f>
         <v>-1,234,500.00%%</v>
@@ -2491,12 +2493,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="9" t="str">
         <f>TEXT(C105, B105)</f>
         <v>0.04%</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="12" t="s">
         <v>126</v>
       </c>
       <c r="C105" s="2">
@@ -2506,7 +2508,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="9" t="str">
         <f t="shared" ref="A107:A110" si="12">TEXT(C107, B107)</f>
         <v>|1.1|</v>
@@ -2521,7 +2523,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="9" t="str">
         <f t="shared" si="12"/>
         <v>| 1.1|</v>
@@ -2536,7 +2538,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="9" t="str">
         <f t="shared" si="12"/>
         <v>|1.1 |</v>
@@ -2551,7 +2553,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="9" t="str">
         <f t="shared" si="12"/>
         <v>| 1.1 |</v>
@@ -2566,7 +2568,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="9" t="str">
         <f>TEXT(C111, B111)</f>
         <v>1,234,567</v>
@@ -2581,7 +2583,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="9" t="str">
         <f>TEXT(C112, B112)</f>
         <v xml:space="preserve">    1,234,567</v>
@@ -2596,7 +2598,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-|1.1|</v>
@@ -2611,7 +2613,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-| 1.1|</v>
@@ -2626,7 +2628,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-|1.1 |</v>
@@ -2641,7 +2643,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="9" t="str">
         <f t="shared" si="0"/>
         <v>-| 1.1 |</v>
@@ -2656,7 +2658,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="9" t="str">
         <f>TEXT(C117, B117)</f>
         <v>-1,234,567</v>
@@ -2671,7 +2673,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="9" t="str">
         <f>TEXT(C118, B118)</f>
         <v>-    1,234,567</v>
@@ -2686,7 +2688,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="9" t="str">
         <f t="shared" si="0"/>
         <v>|23:3/4|</v>
@@ -2701,7 +2703,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="9" t="str">
         <f>TEXT(C121, B121)</f>
         <v>-|23:3/4|</v>
@@ -2716,7 +2718,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="9" t="str">
         <f t="shared" ref="A122" si="13">TEXT(C122, B122)</f>
         <v>|3/4|</v>
@@ -2731,7 +2733,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="9" t="str">
         <f>TEXT(C123, B123)</f>
         <v>-|3/4|</v>
@@ -2746,7 +2748,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="9" t="str">
         <f t="shared" ref="A124:A126" si="14">TEXT(C124, B124)</f>
         <v>|0|</v>
@@ -2761,7 +2763,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="9" t="str">
         <f t="shared" si="14"/>
         <v>|1|</v>
@@ -2776,7 +2778,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="9" t="str">
         <f t="shared" si="14"/>
         <v>-|1|</v>
@@ -2791,7 +2793,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="9" t="str">
         <f t="shared" ref="A127:A134" si="15">TEXT(C127, B127)</f>
         <v>|-2-3:3/4|</v>
@@ -2806,7 +2808,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="9" t="str">
         <f>TEXT(C128, B128)</f>
         <v>-|-2-3:3/4|</v>
@@ -2821,7 +2823,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="9" t="str">
         <f t="shared" ref="A129" si="16">TEXT(C129, B129)</f>
         <v>|--3/4|</v>
@@ -2836,7 +2838,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="9" t="str">
         <f>TEXT(C130, B130)</f>
         <v>-|--3/4|</v>
@@ -2851,7 +2853,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="9" t="str">
         <f t="shared" si="15"/>
         <v>|--0|</v>
@@ -2866,7 +2868,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="9" t="str">
         <f t="shared" si="15"/>
         <v>|--1|</v>
@@ -2881,7 +2883,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="9" t="str">
         <f t="shared" si="15"/>
         <v>-|--1|</v>
@@ -2896,7 +2898,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="9" t="str">
         <f t="shared" si="15"/>
         <v>|23:3=/=4|</v>
@@ -2911,7 +2913,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="9" t="str">
         <f>TEXT(C135, B135)</f>
         <v>-|23:3=/=4|</v>
@@ -2926,7 +2928,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="9" t="str">
         <f t="shared" ref="A136:A139" si="17">TEXT(C136, B136)</f>
         <v>|0|</v>
@@ -2941,7 +2943,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="9" t="str">
         <f t="shared" si="17"/>
         <v>|1|</v>
@@ -2956,7 +2958,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="9" t="str">
         <f t="shared" si="17"/>
         <v>-|1|</v>
@@ -2971,7 +2973,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="9" t="str">
         <f t="shared" si="17"/>
         <v>|23:3=/=4|</v>
@@ -2986,7 +2988,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="9" t="str">
         <f>TEXT(C140, B140)</f>
         <v>-|23:3=/=4|</v>
@@ -3001,7 +3003,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="9" t="str">
         <f t="shared" ref="A141:A144" si="18">TEXT(C141, B141)</f>
         <v>|0      |</v>
@@ -3016,7 +3018,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="9" t="str">
         <f t="shared" si="18"/>
         <v>|1      |</v>
@@ -3031,7 +3033,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="9" t="str">
         <f t="shared" si="18"/>
         <v>-|1      |</v>
@@ -3046,7 +3048,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="9" t="str">
         <f t="shared" si="18"/>
         <v>|23:3=/=4|</v>
@@ -3061,7 +3063,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="9" t="str">
         <f>TEXT(C145, B145)</f>
         <v>-|23:3=/=4|</v>
@@ -3076,7 +3078,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="9" t="str">
         <f t="shared" ref="A146:A148" si="19">TEXT(C146, B146)</f>
         <v>|0|</v>
@@ -3091,7 +3093,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="9" t="str">
         <f t="shared" si="19"/>
         <v>|1|</v>
@@ -3106,7 +3108,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="9" t="str">
         <f t="shared" si="19"/>
         <v>-|1|</v>
@@ -3121,7 +3123,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="9" t="str">
         <f t="shared" si="0"/>
         <v>|2:3 3=/=4|</v>
@@ -3136,7 +3138,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="9" t="str">
         <f>TEXT(C150, B150)</f>
         <v>-|2:3 3=/=4|</v>
@@ -3151,7 +3153,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="9" t="str">
         <f t="shared" si="0"/>
         <v>|:0      |</v>
@@ -3166,7 +3168,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="9" t="str">
         <f t="shared" si="0"/>
         <v>|:1      |</v>
@@ -3181,7 +3183,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="9" t="str">
         <f t="shared" ref="A153:A154" si="20">TEXT(C153, B153)</f>
         <v>-|:1      |</v>
@@ -3196,7 +3198,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="9" t="str">
         <f t="shared" si="20"/>
         <v>|2:3 3=/=4|</v>
@@ -3211,7 +3213,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="9" t="str">
         <f>TEXT(C155, B155)</f>
         <v>-|2:3 3=/=4|</v>
@@ -3226,7 +3228,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="9" t="str">
         <f t="shared" ref="A156:A159" si="21">TEXT(C156, B156)</f>
         <v>|:0      |</v>
@@ -3241,7 +3243,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="9" t="str">
         <f t="shared" si="21"/>
         <v>|:1      |</v>
@@ -3256,7 +3258,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" s="9" t="str">
         <f t="shared" si="21"/>
         <v>-|:1      |</v>
@@ -3271,7 +3273,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" s="9" t="str">
         <f t="shared" si="21"/>
         <v>|2:3  3/4|</v>
@@ -3286,7 +3288,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" s="10" t="str">
         <f t="shared" ref="A160:A162" si="22">TEXT(C160, B160)</f>
         <v>|2:3  03/004</v>
@@ -3301,7 +3303,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" s="9" t="str">
         <f t="shared" si="22"/>
         <v>|   3=/=4|</v>
@@ -3316,7 +3318,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" s="10" t="str">
         <f t="shared" si="22"/>
         <v>|:0  00/001</v>
@@ -3331,7 +3333,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" s="10" t="str">
         <f t="shared" ref="A163:A165" si="23">TEXT(C163, B163)</f>
         <v>|:1  00/001</v>
@@ -3346,7 +3348,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" s="9" t="str">
         <f t="shared" si="23"/>
         <v>|15 /4|</v>
@@ -3361,7 +3363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" s="9" t="str">
         <f>TEXT(C166, B166)</f>
         <v>-|15 /4|</v>
@@ -3376,7 +3378,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" s="9" t="str">
         <f t="shared" ref="A167" si="24">TEXT(C167, B167)</f>
         <v>|3 /4|</v>
@@ -3391,7 +3393,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" s="9" t="str">
         <f>TEXT(C168, B168)</f>
         <v>-|3 /4|</v>
@@ -3406,7 +3408,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" s="9" t="str">
         <f t="shared" ref="A169:A172" si="25">TEXT(C169, B169)</f>
         <v>|0 /1|</v>
@@ -3421,7 +3423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" s="9" t="str">
         <f t="shared" si="25"/>
         <v>|1 /1|</v>
@@ -3436,7 +3438,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" s="9" t="str">
         <f t="shared" si="25"/>
         <v>-|1 /1|</v>
@@ -3451,7 +3453,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" s="9" t="str">
         <f t="shared" si="25"/>
         <v>|15 =/=4|</v>
@@ -3466,7 +3468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" s="9" t="str">
         <f>TEXT(C173, B173)</f>
         <v>-|15 =/=4|</v>
@@ -3481,7 +3483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" s="9" t="str">
         <f t="shared" ref="A174:A177" si="26">TEXT(C174, B174)</f>
         <v>|0 =/=1|</v>
@@ -3496,7 +3498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" s="9" t="str">
         <f t="shared" si="26"/>
         <v>|1 =/=1|</v>
@@ -3511,7 +3513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" s="9" t="str">
         <f t="shared" si="26"/>
         <v>-|1 =/=1|</v>
@@ -3526,7 +3528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" s="9" t="str">
         <f t="shared" si="26"/>
         <v>|15 =/=4|</v>
@@ -3541,7 +3543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="9" t="str">
         <f>TEXT(C178, B178)</f>
         <v>-|15 =/=4|</v>
@@ -3556,7 +3558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" s="9" t="str">
         <f t="shared" ref="A179:A182" si="27">TEXT(C179, B179)</f>
         <v>|0 =/=1|</v>
@@ -3571,7 +3573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" s="9" t="str">
         <f t="shared" si="27"/>
         <v>|1 =/=1|</v>
@@ -3586,7 +3588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" s="9" t="str">
         <f t="shared" si="27"/>
         <v>-|1 =/=1|</v>
@@ -3601,7 +3603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" s="9" t="str">
         <f t="shared" si="27"/>
         <v>|15 =/=4|</v>
@@ -3616,7 +3618,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" s="9" t="str">
         <f>TEXT(C183, B183)</f>
         <v>-|15 =/=4|</v>
@@ -3631,7 +3633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" s="9" t="str">
         <f t="shared" ref="A184:A187" si="28">TEXT(C184, B184)</f>
         <v>|0 =/=1|</v>
@@ -3646,7 +3648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" s="9" t="str">
         <f t="shared" si="28"/>
         <v>|1 =/=1|</v>
@@ -3661,7 +3663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" s="9" t="str">
         <f t="shared" si="28"/>
         <v>-|1 =/=1|</v>
@@ -3676,7 +3678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" s="9" t="str">
         <f t="shared" si="28"/>
         <v>|15 =/=4|</v>
@@ -3691,7 +3693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" s="9" t="str">
         <f>TEXT(C188, B188)</f>
         <v>-|15 =/=4|</v>
@@ -3706,7 +3708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" s="9" t="str">
         <f t="shared" ref="A189:A192" si="29">TEXT(C189, B189)</f>
         <v>|0 =/=1|</v>
@@ -3721,7 +3723,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" s="9" t="str">
         <f t="shared" si="29"/>
         <v>|1 =/=1|</v>
@@ -3736,7 +3738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" s="9" t="str">
         <f t="shared" si="29"/>
         <v>-|1 =/=1|</v>
@@ -3751,7 +3753,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" s="9" t="str">
         <f t="shared" si="29"/>
         <v>|15 =/=4|</v>
@@ -3766,7 +3768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" s="9" t="str">
         <f>TEXT(C193, B193)</f>
         <v>-|15 =/=4|</v>
@@ -3781,7 +3783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" s="9" t="str">
         <f t="shared" ref="A194:A196" si="30">TEXT(C194, B194)</f>
         <v>|0 =/=1|</v>
@@ -3796,7 +3798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="9" t="str">
         <f t="shared" si="30"/>
         <v>|1 =/=1|</v>
@@ -3811,7 +3813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" s="9" t="str">
         <f t="shared" si="30"/>
         <v>-|1 =/=1|</v>
@@ -3826,10 +3828,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D197" s="7"/>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" s="9" t="str">
         <f t="shared" ref="A198:A224" si="31">TEXT(C198, B198)</f>
         <v>|0|</v>
@@ -3844,7 +3846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -3859,7 +3861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0|</v>
@@ -3874,7 +3876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -3889,7 +3891,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -3904,7 +3906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -3919,7 +3921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0=/=1|</v>
@@ -3934,7 +3936,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0=/=1|</v>
@@ -3949,7 +3951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0=/=1|</v>
@@ -3964,7 +3966,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -3979,7 +3981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -3994,7 +3996,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4009,7 +4011,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4024,7 +4026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4039,7 +4041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4054,7 +4056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0:0=/=1|</v>
@@ -4069,7 +4071,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0:0=/=1|</v>
@@ -4084,7 +4086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0:0=/=1|</v>
@@ -4099,7 +4101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0|</v>
@@ -4114,7 +4116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4129,7 +4131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0|</v>
@@ -4144,7 +4146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4159,7 +4161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4174,7 +4176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0      |</v>
@@ -4189,7 +4191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0:0=/=1|</v>
@@ -4204,7 +4206,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0:0=/=1|</v>
@@ -4219,7 +4221,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" s="9" t="str">
         <f t="shared" si="31"/>
         <v>|0:0=/=1|</v>
@@ -4234,7 +4236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225" s="9" t="str">
         <f t="shared" ref="A225:A251" si="32">TEXT(C225, B225)</f>
         <v>|3=/=4|</v>
@@ -4249,7 +4251,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|3=/=4|</v>
@@ -4264,7 +4266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|3=/=4|</v>
@@ -4279,7 +4281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228" s="9" t="str">
         <f t="shared" si="32"/>
         <v>| 3=/=4|</v>
@@ -4294,7 +4296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229" s="9" t="str">
         <f t="shared" si="32"/>
         <v>| 3=/=4|</v>
@@ -4309,7 +4311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" s="9" t="str">
         <f t="shared" si="32"/>
         <v>| 3=/=4|</v>
@@ -4324,7 +4326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|3=/=4|</v>
@@ -4339,7 +4341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|3=/=4|</v>
@@ -4354,7 +4356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|3=/=4|</v>
@@ -4369,7 +4371,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4384,7 +4386,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4399,7 +4401,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4414,7 +4416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4429,7 +4431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4444,7 +4446,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4459,7 +4461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4474,7 +4476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4489,7 +4491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|  3=/=4|</v>
@@ -4504,7 +4506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4519,7 +4521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4534,7 +4536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4549,7 +4551,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4564,7 +4566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4579,7 +4581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4594,7 +4596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4609,7 +4611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4624,7 +4626,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="9" t="str">
         <f t="shared" si="32"/>
         <v>|0:3=/=4|</v>
@@ -4639,7 +4641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="9" t="str">
         <f t="shared" ref="A252:A255" si="33">TEXT(C252, B252)</f>
         <v>|1|</v>
@@ -4654,7 +4656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="9" t="str">
         <f t="shared" si="33"/>
         <v>|1      |</v>
@@ -4669,7 +4671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="9" t="str">
         <f t="shared" si="33"/>
         <v>|1|</v>
@@ -4684,7 +4686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="9" t="str">
         <f t="shared" si="33"/>
         <v>|1      |</v>
@@ -4699,7 +4701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="9" t="str">
         <f t="shared" ref="A256:A264" si="34">TEXT(C256, B256)</f>
         <v>|1      |</v>
@@ -4714,7 +4716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1      |</v>
@@ -4729,7 +4731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1:0=/=1|</v>
@@ -4744,7 +4746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1:0=/=1|</v>
@@ -4759,7 +4761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1:0=/=1|</v>
@@ -4774,7 +4776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1      |</v>
@@ -4789,7 +4791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1      |</v>
@@ -4804,7 +4806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1      |</v>
@@ -4819,7 +4821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="9" t="str">
         <f t="shared" si="34"/>
         <v>|1      |</v>
@@ -4834,7 +4836,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" s="9" t="str">
         <f t="shared" ref="A265:A318" si="35">TEXT(C265, B265)</f>
         <v>|1      |</v>
@@ -4849,7 +4851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1      |</v>
@@ -4864,7 +4866,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1:0=/=1|</v>
@@ -4879,7 +4881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1:0=/=1|</v>
@@ -4894,7 +4896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1:0=/=1|</v>
@@ -4909,7 +4911,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1|</v>
@@ -4924,7 +4926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1      |</v>
@@ -4939,7 +4941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1|</v>
@@ -4954,7 +4956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1      |</v>
@@ -4969,7 +4971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1      |</v>
@@ -4984,7 +4986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1      |</v>
@@ -4999,7 +5001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1:0=/=1|</v>
@@ -5014,7 +5016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1:0=/=1|</v>
@@ -5029,7 +5031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="9" t="str">
         <f t="shared" si="35"/>
         <v>|1:0=/=1|</v>
@@ -5044,7 +5046,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|3=/=4|</v>
@@ -5059,7 +5061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|3=/=4|</v>
@@ -5074,7 +5076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|3=/=4|</v>
@@ -5089,7 +5091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-| 3=/=4|</v>
@@ -5104,7 +5106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-| 3=/=4|</v>
@@ -5119,7 +5121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-| 3=/=4|</v>
@@ -5134,7 +5136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|3=/=4|</v>
@@ -5149,7 +5151,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|3=/=4|</v>
@@ -5164,7 +5166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|3=/=4|</v>
@@ -5179,7 +5181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5194,7 +5196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5209,7 +5211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5224,7 +5226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5239,7 +5241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5254,7 +5256,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5269,7 +5271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5284,7 +5286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5299,7 +5301,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|  3=/=4|</v>
@@ -5314,7 +5316,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5329,7 +5331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5344,7 +5346,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5359,7 +5361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5374,7 +5376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5389,7 +5391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5404,7 +5406,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5419,7 +5421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5434,7 +5436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|0:3=/=4|</v>
@@ -5449,7 +5451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1|</v>
@@ -5464,7 +5466,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5479,7 +5481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1|</v>
@@ -5494,7 +5496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5509,7 +5511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5524,7 +5526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5539,7 +5541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1:0=/=1|</v>
@@ -5554,7 +5556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1:0=/=1|</v>
@@ -5569,7 +5571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1:0=/=1|</v>
@@ -5584,7 +5586,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5599,7 +5601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5614,7 +5616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5629,7 +5631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" s="9" t="str">
         <f t="shared" si="35"/>
         <v>-|1      |</v>
@@ -5644,7 +5646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" s="9" t="str">
         <f t="shared" ref="A319:A332" si="36">TEXT(C319, B319)</f>
         <v>-|1      |</v>
@@ -5659,7 +5661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1      |</v>
@@ -5674,7 +5676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1:0=/=1|</v>
@@ -5689,7 +5691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1:0=/=1|</v>
@@ -5704,7 +5706,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1:0=/=1|</v>
@@ -5719,7 +5721,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1|</v>
@@ -5734,7 +5736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1      |</v>
@@ -5749,7 +5751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1|</v>
@@ -5764,7 +5766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1      |</v>
@@ -5779,7 +5781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1      |</v>
@@ -5794,7 +5796,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1      |</v>
@@ -5809,7 +5811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1:0=/=1|</v>
@@ -5824,7 +5826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1:0=/=1|</v>
@@ -5839,7 +5841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" s="9" t="str">
         <f t="shared" si="36"/>
         <v>-|1:0=/=1|</v>
@@ -5854,7 +5856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" s="9" t="str">
         <f>TEXT(C334, B334)</f>
         <v>314,159.00</v>
@@ -5869,7 +5871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A335" s="9" t="str">
         <f>TEXT(C335, B335)</f>
         <v>$000,314,159</v>
@@ -5884,8 +5886,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C337" s="12"/>
+    <row r="337" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C337" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
